--- a/02_Industrial_OT/IP Address List Rev0.xlsx
+++ b/02_Industrial_OT/IP Address List Rev0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/920e4c882022e26f/Personal Folder/00_Startup/01_Mectosys_Prototype/00_Git_Repo/02_Industrial_OT/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/920e4c882022e26f/Personal Folder/00_Startup/00_MectoSYS_Repo/02_Industrial_OT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{3DF46064-9515-402D-B809-E83203EF3418}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA2EC263-99AB-48A4-AC6B-8812322BDDE2}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{3DF46064-9515-402D-B809-E83203EF3418}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{173767D6-8393-4333-8A9C-383E250ADD66}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="31">
   <si>
     <t>Sr No</t>
   </si>
@@ -85,13 +85,46 @@
   </si>
   <si>
     <t>6ES7 516-3AN00-0AB0</t>
+  </si>
+  <si>
+    <t>Raspberry pi</t>
+  </si>
+  <si>
+    <t>10.193.33.101</t>
+  </si>
+  <si>
+    <t>255.255.255.0</t>
+  </si>
+  <si>
+    <t>S7-1200 PLC</t>
+  </si>
+  <si>
+    <t>10.193.33.6</t>
+  </si>
+  <si>
+    <t>10.193.33.12</t>
+  </si>
+  <si>
+    <t>IOT2050 edge device</t>
+  </si>
+  <si>
+    <t>10.193.33.41</t>
+  </si>
+  <si>
+    <t>Sclance S615</t>
+  </si>
+  <si>
+    <t>6GK5615-0AA00-2AA2</t>
+  </si>
+  <si>
+    <t>6ES7647-0BA00-1YA2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -103,6 +136,12 @@
       <b/>
       <sz val="14"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -484,7 +523,9 @@
       <c r="F2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="1"/>
+      <c r="G2" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="3">
@@ -502,7 +543,9 @@
       <c r="F3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="1"/>
+      <c r="G3" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="3">
@@ -518,7 +561,9 @@
       <c r="F4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="1"/>
+      <c r="G4" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="3">
@@ -534,10 +579,14 @@
       <c r="F5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="1"/>
+      <c r="G5" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="3"/>
+      <c r="B6" s="3">
+        <v>5</v>
+      </c>
       <c r="C6" s="1" t="s">
         <v>17</v>
       </c>
@@ -546,18 +595,30 @@
       <c r="F6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="1"/>
+      <c r="G6" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
+      <c r="B7" s="3">
+        <v>6</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
+      <c r="F7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="1"/>
+      <c r="B8" s="3">
+        <v>7</v>
+      </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
@@ -565,23 +626,45 @@
       <c r="G8" s="1"/>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
+      <c r="B9" s="3">
+        <v>8</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>30</v>
+      </c>
       <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
+      <c r="F9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
+      <c r="B10" s="3">
+        <v>9</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>29</v>
+      </c>
       <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
+      <c r="F10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="1"/>
+      <c r="B11" s="3">
+        <v>10</v>
+      </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
@@ -589,15 +672,27 @@
       <c r="G11" s="1"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
+      <c r="B12" s="3">
+        <v>11</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>30</v>
+      </c>
       <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
+      <c r="F12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="1"/>
+      <c r="B13" s="3">
+        <v>12</v>
+      </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
@@ -605,7 +700,9 @@
       <c r="G13" s="1"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="1"/>
+      <c r="B14" s="3">
+        <v>13</v>
+      </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
@@ -613,7 +710,9 @@
       <c r="G14" s="1"/>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="1"/>
+      <c r="B15" s="3">
+        <v>14</v>
+      </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
@@ -621,7 +720,9 @@
       <c r="G15" s="1"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="1"/>
+      <c r="B16" s="3">
+        <v>15</v>
+      </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
@@ -629,7 +730,9 @@
       <c r="G16" s="1"/>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="1"/>
+      <c r="B17" s="3">
+        <v>16</v>
+      </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
@@ -637,7 +740,9 @@
       <c r="G17" s="1"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="1"/>
+      <c r="B18" s="3">
+        <v>17</v>
+      </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
@@ -645,7 +750,9 @@
       <c r="G18" s="1"/>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="1"/>
+      <c r="B19" s="3">
+        <v>18</v>
+      </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
@@ -653,7 +760,9 @@
       <c r="G19" s="1"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="1"/>
+      <c r="B20" s="3">
+        <v>19</v>
+      </c>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
@@ -717,6 +826,7 @@
       <c r="G27" s="1"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>